--- a/08_Asset_Management/_template_AM.xlsx
+++ b/08_Asset_Management/_template_AM.xlsx
@@ -12,7 +12,8 @@
     <sheet name="Fund NAV" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Fee Waterfall" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Performance Attribution" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="RefreshLog" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Fund Performance" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="RefreshLog" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="68">
   <si>
     <t xml:space="preserve">[FUND] — Asset Management Model</t>
   </si>
@@ -165,6 +166,51 @@
   </si>
   <si>
     <t xml:space="preserve">Total fund return</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fund Performance — LP Reporting Metrics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uses the period cash flows and ending NAV from the Fund NAV tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LP net cash flow (distributions - contributions)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  + terminal NAV added to final period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LP cash flow incl. terminal value (for IRR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumulative capital called</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumulative distributions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current NAV (residual value)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPI (Distributions to Paid-In)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RVPI (Residual Value to Paid-In)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TVPI (Total Value to Paid-In = DPI + RVPI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Headline LP metric — total value (realized + unrealized) per dollar called</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net IRR to LPs (periodic, undated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treats each period as evenly spaced — use XIRR with real dates for called capital at irregular intervals</t>
   </si>
   <si>
     <t xml:space="preserve">Refresh Log</t>
@@ -189,12 +235,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
+    <numFmt numFmtId="167" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -253,6 +300,21 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <i val="true"/>
+      <sz val="8"/>
+      <color rgb="FF808080"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -329,7 +391,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -387,6 +449,22 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -647,7 +725,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:C8"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
@@ -717,7 +795,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:F10"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
@@ -869,7 +947,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:C23"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
@@ -1046,7 +1124,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:F12"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
@@ -1200,8 +1278,182 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B2:F19"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="40"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <f aca="false">'Fund NAV'!C9-'Fund NAV'!C6</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <f aca="false">'Fund NAV'!D9-'Fund NAV'!D6</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <f aca="false">'Fund NAV'!E9-'Fund NAV'!E6</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <f aca="false">'Fund NAV'!F9-'Fund NAV'!F6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <f aca="false">'Fund NAV'!F10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <f aca="false">C7</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <f aca="false">D7</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <f aca="false">E7</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <f aca="false">F7+C8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <f aca="false">SUM('Fund NAV'!C6:F6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <f aca="false">SUM('Fund NAV'!C9:F9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="16" t="n">
+        <f aca="false">'Fund NAV'!F10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="17" t="str">
+        <f aca="false">IFERROR(C14/C13,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="17" t="str">
+        <f aca="false">IFERROR(C15/C13,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="17" t="str">
+        <f aca="false">IFERROR(C16+C17,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="18" t="str">
+        <f aca="false">IFERROR(IRR(C9:F9),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:F14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
@@ -1212,95 +1464,95 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="4" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
